--- a/JsonConverter/ExcelFiles/DialogueGroup.xlsx
+++ b/JsonConverter/ExcelFiles/DialogueGroup.xlsx
@@ -49,7 +49,26 @@
     <t xml:space="preserve">튜토리얼 1_1챕터 그룹</t>
   </si>
   <si>
-    <t xml:space="preserve">dialogue_tutorial_1_1_100</t>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="&quot;맑은 고딕&quot;"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">dialogue_tutorial_1_1_001, </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="&quot;맑은 고딕&quot;"/>
+        <family val="0"/>
+        <charset val="129"/>
+      </rPr>
+      <t xml:space="preserve">dialogue_tutorial_1_1_002, dialogue_tutorial_1_1_003</t>
+    </r>
   </si>
   <si>
     <t xml:space="preserve">dialogue_group_mainstream_1_1</t>
